--- a/publication_tables/supplementary/S9_policy_rankings.xlsx
+++ b/publication_tables/supplementary/S9_policy_rankings.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>energy_only</t>
+          <t>consumption_CD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>energy_support_only</t>
+          <t>consumption_flat_CES2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,7 +504,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fixed_negative_investment</t>
+          <t>energy_only</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -523,7 +523,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>food_only</t>
+          <t>energy_support_only</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -542,7 +542,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>high_admin</t>
+          <t>fixed_negative_investment</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -561,7 +561,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>high_budget</t>
+          <t>food_only</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -580,7 +580,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>high_factor_elasticity</t>
+          <t>high_admin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -599,7 +599,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>high_trade_elasticity</t>
+          <t>high_budget</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -618,7 +618,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>low_budget</t>
+          <t>high_factor_elasticity</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -637,7 +637,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>low_factor_elasticity</t>
+          <t>high_trade_elasticity</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -656,7 +656,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>low_trade_elasticity</t>
+          <t>high_within_substitution</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -675,7 +675,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>low_budget</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -694,7 +694,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mild_joint</t>
+          <t>low_factor_elasticity</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -713,7 +713,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>severe_joint</t>
+          <t>low_trade_elasticity</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -732,7 +732,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>symmetric_world_prices</t>
+          <t>low_within_substitution</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -751,19 +751,133 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mild_joint</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>severe_joint</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>symmetric_world_prices</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>zero_admin</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -778,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,238 +1186,310 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scenario: energy_only</t>
+          <t>Scenario: consumption_CD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Energy import prices +40%; no food import-price shock.</t>
+          <t>Cobb-Douglas consumption (elasticity 1) in both CGE and microsimulation; all other main settings unchanged.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scenario: energy_support_only</t>
+          <t>Scenario: consumption_flat_CES2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Consumer price support applies only to energy sectors S09 (C19) and S23 (D35).</t>
+          <t>Single-level CES consumption with elasticity 2 in CGE and microsimulation.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scenario: fixed_negative_investment</t>
+          <t>Scenario: energy_only</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The five negative net investment quantities remain at benchmark levels; positive components absorb investment adjustment.</t>
+          <t>Energy import prices +40%; no food import-price shock.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scenario: food_only</t>
+          <t>Scenario: energy_support_only</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Food import prices +20%; no energy import-price shock.</t>
+          <t>Consumer price support applies only to energy sectors S09 (C19) and S23 (D35).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scenario: high_admin</t>
+          <t>Scenario: fixed_negative_investment</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Administration absorbs 10% of gross cash-programme expenditure.</t>
+          <t>The five negative net investment quantities remain at benchmark levels; positive components absorb investment adjustment.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scenario: high_budget</t>
+          <t>Scenario: food_only</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Net fiscal cost is 1% of benchmark GDP.</t>
+          <t>Food import prices +20%; no energy import-price shock.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scenario: high_factor_elasticity</t>
+          <t>Scenario: high_admin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>All capital–labour CES elasticities ω are multiplied by 1.25.</t>
+          <t>Administration absorbs 10% of gross cash-programme expenditure.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scenario: high_trade_elasticity</t>
+          <t>Scenario: high_budget</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>All Armington σ and CET ψ values are multiplied by 1.25.</t>
+          <t>Net fiscal cost is 1% of benchmark GDP.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scenario: low_budget</t>
+          <t>Scenario: high_factor_elasticity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Net fiscal cost is 0.25% of benchmark GDP.</t>
+          <t>All capital–labour CES elasticities ω are multiplied by 1.25.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Scenario: low_factor_elasticity</t>
+          <t>Scenario: high_trade_elasticity</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>All capital–labour CES elasticities ω are multiplied by 0.75.</t>
+          <t>All Armington σ and CET ψ values are multiplied by 1.25.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scenario: low_trade_elasticity</t>
+          <t>Scenario: high_within_substitution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>All Armington σ and CET ψ values are multiplied by 0.75.</t>
+          <t>Within-nest elasticities are food 1.00, energy 0.80 and other 1.00; upper-nest elasticity remains 0.25.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scenario: main</t>
+          <t>Scenario: low_budget</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Food import prices +20%; energy import prices +40%; net fiscal cost 0.5% of benchmark GDP; administration 3% of gross cash-programme spending. Uses benchmark sector elasticities, signed investment shares and full consumption of new cash.</t>
+          <t>Net fiscal cost is 0.25% of benchmark GDP.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scenario: mild_joint</t>
+          <t>Scenario: low_factor_elasticity</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Milder joint shock: food +10%, energy +20%.</t>
+          <t>All capital–labour CES elasticities ω are multiplied by 0.75.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scenario: severe_joint</t>
+          <t>Scenario: low_trade_elasticity</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>More severe joint shock: food +40%, energy +80%.</t>
+          <t>All Armington σ and CET ψ values are multiplied by 0.75.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scenario: symmetric_world_prices</t>
+          <t>Scenario: low_within_substitution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>World export prices in shocked sectors increase by the same rates as their world import prices.</t>
+          <t>Within-nest elasticities are food 0.25, energy 0.20 and other 0.25; upper-nest elasticity remains 0.25.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scenario: zero_admin</t>
+          <t>Scenario: main</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The cash-programme administration rate is zero.</t>
+          <t>Food import prices +20%; energy import prices +40%; net fiscal cost 0.5% of benchmark GDP; administration 3% of gross cash-programme spending. Uses benchmark sector elasticities, signed investment shares and full consumption of new cash.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Policy: perfect_targeting</t>
+          <t>Scenario: mild_joint</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+          <t>Milder joint shock: food +10%, energy +20%.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Policy: pmt</t>
+          <t>Scenario: severe_joint</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+          <t>More severe joint shock: food +40%, energy +80%.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Policy: universal_cash</t>
+          <t>Scenario: symmetric_world_prices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Universal cash: equal per-person payment to every represented person.</t>
+          <t>World export prices in shocked sectors increase by the same rates as their world import prices.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Scenario: upper_substitution_050</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Food-energy-other upper-nest elasticity is 0.50; within-nest elasticities retain their main values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Scenario: upper_substitution_085</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Food-energy-other upper-nest elasticity is 0.85; within-nest elasticities retain their main values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Scenario: zero_admin</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The cash-programme administration rate is zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Policy: perfect_targeting</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Perfectly targeted cash: equal per-person payments to everyone in the lowest two benchmark income groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Policy: pmt</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Out-of-fold proxy means test (PMT): recipients selected by predicted income; coverage equals target-population size; equal per-person payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Policy: universal_cash</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Universal cash: equal per-person payment to every represented person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Policy: price_support</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Price support: a common proportional discount on eligible household purchases, solved at the same final net fiscal cost.</t>
         </is>
